--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE13154-4E95-4D4A-859E-3DD5634E7CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146841E2-E8A4-492C-9CDB-84DA48E360F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8070" yWindow="8880" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22035" yWindow="-1935" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>1</v>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146841E2-E8A4-492C-9CDB-84DA48E360F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1981BC-86BE-470D-BC0F-0A82740AD9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22035" yWindow="-1935" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21600" yWindow="-1770" windowWidth="32715" windowHeight="35145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -778,7 +778,7 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -797,7 +797,7 @@
         <v>2</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -816,7 +816,7 @@
         <v>6</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <v>1101</v>
